--- a/data-tables/Datas/constants.xlsx
+++ b/data-tables/Datas/constants.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -510,10 +510,23 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
+          <t>starting_shell</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>starting_prestige_point</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
